--- a/docs/Catalogo-y-Balance-Juego-Torre-De-Cartas.xlsx
+++ b/docs/Catalogo-y-Balance-Juego-Torre-De-Cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santi\Documents\desarrollo_orientado_plataformas\torre-de-cartas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80717C71-8B90-41D8-92F7-35D068AC868D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DBCB3D-10DE-40FA-B904-12211E85DE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9B76173C-9502-48F9-B168-55AE19AB37B7}"/>
   </bookViews>
@@ -54,191 +54,225 @@
     <t>Rarezas</t>
   </si>
   <si>
-    <t>Nombre: Ataque Basico
+    <t>Rara
+cant = 2</t>
+  </si>
+  <si>
+    <t>Legendaria
+cant = 1</t>
+  </si>
+  <si>
+    <t>Duplicados</t>
+  </si>
+  <si>
+    <t>Ataque Neto</t>
+  </si>
+  <si>
+    <t>Defensa Neta</t>
+  </si>
+  <si>
+    <t>Total Cant:</t>
+  </si>
+  <si>
+    <t>Total:</t>
+  </si>
+  <si>
+    <t>Promedio Val:</t>
+  </si>
+  <si>
+    <t>Poco común
+cant: = 3</t>
+  </si>
+  <si>
+    <t>Común
+cant: &gt; 3</t>
+  </si>
+  <si>
+    <t>id_carta: 1
+Nombre: Ataque Básico
 Valor: 1
+Tipo: Ataque
 Efecto: Ninguno
 Cantidad: 4
-Rareza: Comun
-Descripcion: Inflige 1 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Defensa Basica
-Valor: 1
-Efecto: Ninguno
-Cantidad: 4
-Rareza: Comun
-Descripcion: Cubre 1 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Curacion simple
-Valor: 1
-Efecto: Ninguno 
-Cantidad: 4
-Rareza: Comun
-Descripcion: Cura 1 unidad</t>
-  </si>
-  <si>
-    <t>Comun
-cant: &gt; 3</t>
-  </si>
-  <si>
-    <t>Nombre: Ataque Normal
+Rareza: Común
+Descripción: Inflige 1 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 2
+Nombre: Ataque Normal
 Valor: 2
+Tipo: Ataque
 Efecto: Ninguno
 Cantidad: 3
-Rareza: Poco comun
-Descripcion: Inflige 3 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Defensa Normal
-Valor: 2
-Efecto: Ninguno
-Cantidad: 3
-Rareza: Poco comun
-Descripcion: Cubre 3 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Curacion Normal
-Valor: 2
-Efecto: Ninguno 
-Cantidad: 3
-Rareza: Poco comun
-Descripcion: Cura tres unidades</t>
-  </si>
-  <si>
-    <t>Poco comun
-cant: = 3</t>
-  </si>
-  <si>
-    <t>Nombre: Ataque Fuerte
+Rareza: Poco común
+Descripción: Inflige 2 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 3
+Nombre: Ataque Fuerte
 Valor: 3
+Tipo: Ataque
 Efecto: Ninguno
 Cantidad: 2
 Rareza: Rara
-Descripcion: Inflige 3 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Defensa Fuerte
+Descripción: Inflige 3 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 4
+Nombre: Ataque Devastador
+Valor: 5
+Tipo: Ataque
+Efecto: Ninguno
+Cantidad: 1
+Rareza: Legendaria
+Descripción: Inflige 5 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 5
+Nombre: Defensa Básica
+Valor: 1
+Tipo: Defensa
+Efecto: Ninguno
+Cantidad: 4
+Rareza: Común
+Descripción: Cubre 1 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 6
+Nombre: Defensa Normal
+Valor: 2
+Tipo: Defensa
+Efecto: Ninguno
+Cantidad: 3
+Rareza: Poco común
+Descripción: Cubre 2 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 7
+Nombre: Defensa Fuerte
 Valor: 3
+Tipo: Defensa
 Efecto: Ninguno
 Cantidad: 2
 Rareza: Rara
-Descripcion: Cubre 3 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Curacion Fuerte
+Descripción: Cubre 3 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 8
+Nombre: Defensa Implacable
+Valor: 5
+Tipo: Defensa
+Efecto: Ninguno
+Cantidad: 1
+Rareza: Legendaria
+Descripción: Cubre 5 de daño.</t>
+  </si>
+  <si>
+    <t>id_carta: 9
+Nombre: Curación Básica
+Valor: 1
+Tipo: Especial
+Efecto: Ninguno 
+Cantidad: 4
+Rareza: Común
+Descripción: Cura 1 unidad.</t>
+  </si>
+  <si>
+    <t>id_carta: 10
+Nombre: Curación Normal
+Valor: 2
+Tipo: Especial
+Efecto: Ninguno 
+Cantidad: 3
+Rareza: Poco común
+Descripción: Cura 2 unidades.</t>
+  </si>
+  <si>
+    <t>id_carta: 11
+Nombre: Curación Fuerte
 Valor: 3
+Tipo: Especial
 Efecto: Ninguno 
 Cantidad: 2
 Rareza: Rara
-Descripcion: Cura 3 unidades</t>
-  </si>
-  <si>
-    <t>Rara
-cant = 2</t>
-  </si>
-  <si>
-    <t>Nombre: Ataque devastador
+Descripción: Cura 3 unidades.</t>
+  </si>
+  <si>
+    <t>id_carta: 12
+Nombre: Curación Vigorosa
 Valor: 5
+Tipo: Especial
 Efecto: Ninguno
 Cantidad: 1
 Rareza: Legendaria
-Descripcion: Inflige 5 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Defensa implacable
-Valor: 5
-Efecto: Ninguno
-Cantidad: 1
-Rareza: Legendaria
-Descripcion: Cubre 5 de daño</t>
-  </si>
-  <si>
-    <t>Nombre: Curación vigorosa
-Valor: 5
-Efecto: Ninguno
-Cantidad: 1
-Rareza: Legendaria
-Descripcion: Cura 5 unidades</t>
-  </si>
-  <si>
-    <t>Legendaria
-cant = 1</t>
-  </si>
-  <si>
-    <t>Nombre: Masa Crítica
+Descripción: Cura 5 unidades.</t>
+  </si>
+  <si>
+    <t>id_carta: 13
+Nombre: Masa Crítica
 Valor: 0
+Tipo: Especial
 Efecto: Genera daño por la cantidad
 de cartas de tipo daño en la mano.
 Cantidad: 2
 Rareza: Rara
-Descripcion: Usa todas tus armas
+Descripción: Usa todas tus armas
 contra el enemigo.</t>
   </si>
   <si>
-    <t>Nombre: Muro de Contención
+    <t>id_carta: 14
+Nombre: Muro de Contención
 Valor: 0
+Tipo: Especial
 Efecto: Genera defensa por la cantidad
 de cartas de tipo defensa en la mano.
 Cantidad: 2
 Rareza: Rara
-Descripcion: Usa todas tus defensas
+Descripción: Usa todas tus defensas
 para tu fortaleza.</t>
   </si>
   <si>
-    <t>Nombre: Infiltración
+    <t>id_carta: 15
+Nombre: Infiltración
 Valor: 0
+Tipo: Especial
 Efecto: Revela la mano de tu enemigo.
 Cantidad: 2
 Rareza: Rara
-Descripcion: Que tu enemigo quede
+Descripción: Que tu enemigo quede
 al desnudo.</t>
   </si>
   <si>
-    <t>Nombre: Reinicio Táctico
+    <t>id_carta: 16
+Nombre: Reinicio Táctico
 Valor: 0
-Efecto: Cambia todas tus cartas
-al deznudo.
+Tipo: Especial
+Efecto: Cambia todas tus cartas por nuevas.
 Cantidad: 2
 Rareza: Rara
-Descripcion: Borrón y cartas nuevas.</t>
-  </si>
-  <si>
-    <t>Nombre: Desarme
+Descripción: Borrón y cartas nuevas.</t>
+  </si>
+  <si>
+    <t>id_carta: 17
+Nombre: Desarme
 Valor: 0
+Tipo: Especial
 Efecto: El enemigo pierde una carta
 de su mano.
 Cantidad: 2
 Rareza: Rara
-Descripcion: Deja al enemigo sin garras.</t>
-  </si>
-  <si>
-    <t>Nombre: Caja de Suministros:
+Descripción: Deja al enemigo sin garras.</t>
+  </si>
+  <si>
+    <t>id_carta: 18
+Nombre: Caja de Suministros:
 Valor: 0
+Tipo: Especial
 Efecto: Consigues dos cartas de tu mazo.
 Cantidad: 2
 Rareza: Rara
-Descripcion: Asegurate de tener tu mano
-con dos espacios libres antes de usarla, no
-quieres desperdiciar esta carta.</t>
-  </si>
-  <si>
-    <t>Duplicados</t>
-  </si>
-  <si>
-    <t>Ataque Neto</t>
-  </si>
-  <si>
-    <t>Defensa Neta</t>
-  </si>
-  <si>
-    <t>Total Cant:</t>
-  </si>
-  <si>
-    <t>Total:</t>
-  </si>
-  <si>
-    <t>Promedio Val:</t>
+Descripción: Asegúrate de tener tu mano
+con dos espacios libres antes de usarla, no quieres desperdiciar esta carta.</t>
   </si>
 </sst>
 </file>
@@ -542,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -606,6 +640,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -940,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{796286C3-5B21-4F03-90EB-FD788B9E7A1B}">
-  <dimension ref="B2:I12"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" customWidth="1"/>
@@ -952,7 +987,7 @@
     <col min="8" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -969,137 +1004,139 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>4</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I6" s="14"/>
     </row>
-    <row r="7" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="150" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>5</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="150" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>6</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="135" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>7</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>8</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="135" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>9</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="165" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>10</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1120,7 +1157,7 @@
     <col min="14" max="14" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B2" s="16" t="s">
         <v>1</v>
@@ -1129,13 +1166,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1195,7 +1232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="23">
         <v>5</v>
       </c>
@@ -1214,9 +1251,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B7" s="27">
         <f>D3+D4+D5+D6</f>
@@ -1231,7 +1268,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G7" s="30">
         <f>G3+G4+G5+G6</f>
@@ -1242,9 +1279,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B8" s="33">
         <f>(G3+G4+G5+G6)/B7</f>
